--- a/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
+++ b/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
@@ -485,20 +485,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="63" customWidth="1" min="4" max="4"/>
-    <col width="75" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="75" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3772</v>
+        <v>938</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>882</v>
+        <v>1433</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>278</v>
+        <v>376</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>264</v>
+        <v>376</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>737</v>
+        <v>879</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>815</v>
+        <v>914</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>941</v>
+        <v>844</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>838</v>
+        <v>933</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>815</v>
+        <v>877</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>731</v>
+        <v>918</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>766</v>
+        <v>867</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>694</v>
+        <v>1021</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>758</v>
+        <v>940</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>711</v>
+        <v>786</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>734</v>
+        <v>930</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>849</v>
+        <v>931</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>772</v>
+        <v>878</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>887</v>
+        <v>944</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>743</v>
+        <v>845</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>881</v>
+        <v>942</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>835</v>
+        <v>872</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>562</v>
+        <v>794</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>633</v>
+        <v>820</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>625</v>
+        <v>785</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>598</v>
+        <v>825</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>685</v>
+        <v>921</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>754</v>
+        <v>822</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>737</v>
+        <v>703</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>615</v>
+        <v>806</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>668</v>
+        <v>765</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>808</v>
+        <v>775</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>719</v>
+        <v>847</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>682</v>
+        <v>914</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>625</v>
+        <v>805</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>663</v>
+        <v>813</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>598</v>
+        <v>760</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>652</v>
+        <v>782</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>644</v>
+        <v>768</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>693</v>
+        <v>766</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>GitHub Release (DA 96)</t>
+          <t>GitHub Release v1.0 (DA 96)</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>717</v>
+        <v>766</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>638</v>
+        <v>795</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>658</v>
+        <v>759</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>605</v>
+        <v>779</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1080</v>
+        <v>802</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>643</v>
+        <v>1046</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>665</v>
+        <v>858</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>647</v>
+        <v>1118</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>749</v>
+        <v>806</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>631</v>
+        <v>765</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>698</v>
+        <v>772</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>768</v>
+        <v>807</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>721</v>
+        <v>789</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>682</v>
+        <v>836</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>664</v>
+        <v>768</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>724</v>
+        <v>758</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>701</v>
+        <v>779</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>635</v>
+        <v>920</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>GitHub Issue (DA 96)</t>
+          <t>GitHub Issue #1 (DA 96)</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>663</v>
+        <v>792</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>547</v>
+        <v>764</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>557</v>
+        <v>806</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>532</v>
+        <v>680</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>532</v>
+        <v>775</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>540</v>
+        <v>800</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>506</v>
+        <v>880</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>616</v>
+        <v>724</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>587</v>
+        <v>799</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>629</v>
+        <v>872</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>598</v>
+        <v>680</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>516</v>
+        <v>875</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>576</v>
+        <v>692</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>569</v>
+        <v>680</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>567</v>
+        <v>691</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>661</v>
+        <v>709</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>579</v>
+        <v>676</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>553</v>
+        <v>667</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>576</v>
+        <v>772</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>572</v>
+        <v>699</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>GitHub Gist (DA 96)</t>
+          <t>GitHub Gist Wave 1 (DA 96)</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>565</v>
+        <v>686</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>388</v>
+        <v>1367</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>383</v>
+        <v>287</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>442</v>
+        <v>272</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>365</v>
+        <v>260</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>385</v>
+        <v>252</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>382</v>
+        <v>285</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>462</v>
+        <v>287</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>391</v>
+        <v>348</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>371</v>
+        <v>281</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>386</v>
+        <v>253</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>449</v>
+        <v>270</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>377</v>
+        <v>245</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>392</v>
+        <v>300</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>389</v>
+        <v>297</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>376</v>
+        <v>249</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>382</v>
+        <v>286</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>382</v>
+        <v>269</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>100</v>
+        <v>412</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>579</v>
+        <v>897</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>449</v>
+        <v>510</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>497</v>
+        <v>389</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>564</v>
+        <v>411</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>482</v>
+        <v>543</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>591</v>
+        <v>405</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G119" s="2" t="n">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>453</v>
+        <v>533</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>468</v>
+        <v>611</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>466</v>
+        <v>2250</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>472</v>
+        <v>1171</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>491</v>
+        <v>394</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN (DA 96)</t>
+          <t>GitHub Raw CDN Docs (DA 96)</t>
         </is>
       </c>
       <c r="G127" s="2" t="n">
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>445</v>
+        <v>408</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>527</v>
+        <v>221</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1077</v>
+        <v>1221</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>426</v>
+        <v>900</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>701</v>
+        <v>76</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>403</v>
+        <v>1079</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>424</v>
+        <v>895</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>462</v>
+        <v>921</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>387</v>
+        <v>167</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>399</v>
+        <v>902</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>206</v>
+        <v>560</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>85</v>
+        <v>425</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>491</v>
+        <v>98</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>418</v>
+        <v>198</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>665</v>
+        <v>115</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1218</v>
+        <v>1472</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>165</v>
+        <v>932</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>188</v>
+        <v>548</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1542</v>
+        <v>1271</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>389</v>
+        <v>1023</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>481</v>
+        <v>358</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>389</v>
+        <v>100</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>380</v>
+        <v>868</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>370</v>
+        <v>66</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>407</v>
+        <v>1151</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>641</v>
+        <v>867</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>402</v>
+        <v>596</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>569</v>
+        <v>68</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>612</v>
+        <v>563</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>438</v>
+        <v>638</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>678</v>
+        <v>85</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>484</v>
+        <v>98</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>411</v>
+        <v>62</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>667</v>
+        <v>809</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>387</v>
+        <v>803</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>272</v>
+        <v>556</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1012</v>
+        <v>889</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -9021,6 +9021,5106 @@
       <c r="K167" s="3" t="inlineStr">
         <is>
           <t>FounderRunway RSS Channel Feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/44972a0946304b11e233b7a108fb4b6f</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>713</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: LocalAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/b089bc8abf5cc1e5c52cca00013af8d5</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>655</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: WorkationRadar</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/1d75226a73dd0946b1bc34f8b46c1057</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: OpenAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/0a251d0c8e6b9f2a0f3abf3300c649b8</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>772</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: IndieStackAudit</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/95c504bd303e2c977edf21c8b6b57dc7</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: VectorBench</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/ad283f0b9e7876f27c0e9bfbb72a84b1</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: NomadTreaty</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/9f4ac3b6d9a9e3a45de07e42cb640db8</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>642</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: WebhookWatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/d5dc9ce8ae43b1fc340559f429f271c7</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: LocalDocPrivacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/a6662e75d77903b10a4b1ebad7980552</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: FounderRunway</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/73a1d629f768652ee3dd118c32125e89</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: RAGInspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/9ff0582a3875ab1e6099f60e274e047f</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: NomadPassportIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/05b4e36b0f72746030acbb2dab764bb6</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>654</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: SaaSUnitMath</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/40954241eb38a9f8fa15a778de068e49</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>1751</v>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: GrokLogTester</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/e232037e300eb528644c54c9054f221a</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: SOC2Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/2eaa7f57ab6afd9e3bc98e3b18fcaa70</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>721</v>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: EORCalculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/998e635ae0ad22da8365dc6164a265ab</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>644</v>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: DevConfigHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/5aafd5358dfecc9c288cba38af2f83af</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: OpenCRMStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/e610888dae1f1ade5cab84eaff33f5c2</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>677</v>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: CIPipelineGraph</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/f4ed3fdd7c2f6180f92cc3292406ecc5</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: GreekVisualizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/d74d051655c989c7d9f0677f4c790c46</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 2 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>647</v>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: EdgeRuntimeHQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/local-agent-hardware-stack/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/workation-coliving-radar/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/open-agent-protocol-hub/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/indie-saas-stack-audit/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>748</v>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/vector-database-benchmarks/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>812</v>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/nomad-tax-treaty-calculator/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>839</v>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/webhook-signature-audit/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>926</v>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/local-pdf-privacy-redactor/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/founder-runway-calculator/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>772</v>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/rag-semantic-chunking-bench/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/nomad-passport-visa-index/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/saas-unit-economics-calculator/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/nginx-grok-log-tester/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/soc2-readiness-checklist/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/global-eor-payroll-calculator/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/devcontainer-docker-generator/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/open-crm-migration-tco/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>886</v>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/github-actions-dag-validator/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/options-greeks-visualizer/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="n">
+        <v>732</v>
+      </c>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/webgpu-edge-inference-bench/releases/tag/v1.1.0</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Release v1.1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="n">
+        <v>757</v>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ v1.1.0 Advanced Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/local-agent-hardware-stack/issues/2</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="n">
+        <v>773</v>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (LocalAgentStack)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/workation-coliving-radar/issues/2</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (WorkationRadar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/open-agent-protocol-hub/issues/2</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (OpenAgentStack)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/indie-saas-stack-audit/issues/2</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (IndieStackAudit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/vector-database-benchmarks/issues/2</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="n">
+        <v>891</v>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (VectorBench)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/nomad-tax-treaty-calculator/issues/2</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (NomadTreaty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/webhook-signature-audit/issues/2</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="n">
+        <v>869</v>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (WebhookWatch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/local-pdf-privacy-redactor/issues/2</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="n">
+        <v>761</v>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (LocalDocPrivacy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/founder-runway-calculator/issues/2</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (FounderRunway)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/rag-semantic-chunking-bench/issues/2</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="n">
+        <v>804</v>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (RAGInspect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/nomad-passport-visa-index/issues/2</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="n">
+        <v>757</v>
+      </c>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (NomadPassportIndex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/saas-unit-economics-calculator/issues/2</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (SaaSUnitMath)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/nginx-grok-log-tester/issues/2</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (GrokLogTester)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/soc2-readiness-checklist/issues/2</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (SOC2Ready)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/global-eor-payroll-calculator/issues/2</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (EORCalculator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/devcontainer-docker-generator/issues/2</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (DevConfigHub)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/open-crm-migration-tco/issues/2</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (OpenCRMStack)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/github-actions-dag-validator/issues/2</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (CIPipelineGraph)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/options-greeks-visualizer/issues/2</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (GreekVisualizer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jibranpcccc/webgpu-edge-inference-bench/issues/2</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Issue #2 RFC (DA 96)</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>RFC #2: Architecture Spec (EdgeRuntimeHQ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-1-localagentstack.html</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>Launch LocalAgentStack Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-2-workationradar.html</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>Launch WorkationRadar Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-3-openagentstack.html</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>Launch OpenAgentStack Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-4-indiestackaudit.html</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>Launch IndieStackAudit Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-5-vectorbench.html</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>Launch VectorBench Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-6-nomadtreaty.html</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>Launch NomadTreaty Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-7-webhookwatch.html</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>Launch WebhookWatch Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-8-localdocprivacy.html</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>Launch LocalDocPrivacy Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-9-founderrunway.html</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>Launch FounderRunway Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-10-raginspect.html</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="J237" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>Launch RAGInspect Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-11-nomadpassportindex.html</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>Launch NomadPassportIndex Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-12-saasunitmath.html</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>Launch SaaSUnitMath Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-13-groklogtester.html</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>Launch GrokLogTester Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-14-soc2ready.html</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>Launch SOC2Ready Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-15-eorcalculator.html</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>Launch EORCalculator Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-16-devconfighub.html</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>Launch DevConfigHub Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-17-opencrmstack.html</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>Launch OpenCRMStack Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-18-cipipelinegraph.html</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>Launch CIPipelineGraph Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-19-greekvisualizer.html</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="J246" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>Launch GreekVisualizer Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/benchmarks/site-20-edgeruntimehq.html</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages Benchmark Hub (DA 96)</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="J247" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>Launch EdgeRuntimeHQ Live Tool &amp; Specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/local-agent-hardware-stack/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: LocalAgentStack (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/workation-coliving-radar/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="J249" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: WorkationRadar (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/open-agent-protocol-hub/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: OpenAgentStack (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/indie-saas-stack-audit/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: IndieStackAudit (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/vector-database-benchmarks/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: VectorBench (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/nomad-tax-treaty-calculator/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: NomadTreaty (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/webhook-signature-audit/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="n">
+        <v>353</v>
+      </c>
+      <c r="J254" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: WebhookWatch (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/local-pdf-privacy-redactor/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: LocalDocPrivacy (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/founder-runway-calculator/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="J256" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: FounderRunway (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/rag-semantic-chunking-bench/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: RAGInspect (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/nomad-passport-visa-index/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="J258" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: NomadPassportIndex (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/saas-unit-economics-calculator/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="J259" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: SaaSUnitMath (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/nginx-grok-log-tester/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="J260" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: GrokLogTester (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/soc2-readiness-checklist/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="J261" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: SOC2Ready (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/global-eor-payroll-calculator/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="J262" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: EORCalculator (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/devcontainer-docker-generator/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="J263" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: DevConfigHub (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="20" customHeight="1">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/open-crm-migration-tco/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: OpenCRMStack (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="20" customHeight="1">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/github-actions-dag-validator/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: CIPipelineGraph (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/options-greeks-visualizer/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: GreekVisualizer (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/webgpu-edge-inference-bench/main/BENCHMARKS.md</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN Benchmarks (DA 96)</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="J267" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>Empirical Benchmarks: EdgeRuntimeHQ (Raw CDN)</t>
         </is>
       </c>
     </row>
@@ -9140,19 +14240,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>1</v>
@@ -9161,7 +14261,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
@@ -9189,19 +14289,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>1</v>
@@ -9210,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
@@ -9238,19 +14338,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>1</v>
@@ -9259,7 +14359,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -9287,19 +14387,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>1</v>
@@ -9308,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
@@ -9336,19 +14436,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>1</v>
@@ -9357,7 +14457,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
@@ -9385,19 +14485,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>1</v>
@@ -9406,7 +14506,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
@@ -9434,19 +14534,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>1</v>
@@ -9455,7 +14555,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
@@ -9483,19 +14583,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>1</v>
@@ -9504,7 +14604,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
@@ -9532,19 +14632,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>1</v>
@@ -9553,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
@@ -9581,19 +14681,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>1</v>
@@ -9602,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
@@ -9630,19 +14730,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>1</v>
@@ -9651,7 +14751,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
@@ -9679,19 +14779,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>1</v>
@@ -9700,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
@@ -9728,19 +14828,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>1</v>
@@ -9749,7 +14849,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
@@ -9777,19 +14877,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>1</v>
@@ -9798,7 +14898,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
@@ -9826,19 +14926,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>1</v>
@@ -9847,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
@@ -9875,19 +14975,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>1</v>
@@ -9896,7 +14996,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
@@ -9924,19 +15024,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>1</v>
@@ -9945,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
@@ -9973,19 +15073,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>1</v>
@@ -9994,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
@@ -10022,19 +15122,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>1</v>
@@ -10043,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
@@ -10071,19 +15171,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>1</v>
@@ -10092,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
@@ -10111,15 +15211,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -10130,7 +15230,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Domain / Path</t>
+          <t>Domain / Path Pattern</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -10150,7 +15250,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Search Engine Indexing Velocity</t>
+          <t>Search Engine Discovery Speed</t>
         </is>
       </c>
     </row>
@@ -10177,7 +15277,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Homepage Metadata</t>
+          <t>Dofollow Homepage Metadata &amp; README</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -10194,7 +15294,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../releases/tag/*</t>
+          <t>github.com/.../releases/tag/v1.0.0</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -10221,12 +15321,12 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GitHub Official Issues / Specs</t>
+          <t>GitHub v1.1.0 Advanced Releases</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../issues/1</t>
+          <t>github.com/.../releases/tag/v1.1.0</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -10241,24 +15341,24 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Technical Tracker</t>
+          <t>Empirical Benchmarks Release Notes</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>12–24 Hours</t>
+          <t>24–48 Hours</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Public GitHub Gists</t>
+          <t>GitHub Official Issues #1 (Specs)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>gist.github.com/jibranpcccc/*</t>
+          <t>github.com/.../issues/1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -10273,24 +15373,24 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Runnable Code Snippets</t>
+          <t>Dofollow Technical Tracker &amp; Specs</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>24–48 Hours</t>
+          <t>12–24 Hours</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Dedicated Profiles</t>
+          <t>GitHub Technical RFC Issues #2</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/tools/*</t>
+          <t>github.com/.../issues/2</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -10305,24 +15405,24 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Dofollow CTA &amp; Directory Profile</t>
+          <t>Official Architecture RFC Specification</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>12–24 Hours</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN Documentation</t>
+          <t>Public GitHub Gists (Wave 1)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>raw.githubusercontent.com/*</t>
+          <t>gist.github.com/jibranpcccc/*</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -10337,24 +15437,24 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Direct Markdown API Endpoints</t>
+          <t>Dofollow Runnable Code Snippets</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>24–48 Hours</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GitHub Profile Portfolio Hub</t>
+          <t>Public GitHub Gists (Wave 2)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>github.com/jibranpcccc</t>
+          <t>gist.github.com/jibranpcccc/*</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -10364,29 +15464,29 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Sitewide Showcase</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Technical Portfolio</t>
+          <t>Deep-Tech Runnable Guides &amp; Math</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>24–48 Hours</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GitHub Monorepo Index</t>
+          <t>GitHub Pages Tools Directory</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../digitalcreatoravi-seo-engine</t>
+          <t>jibranpcccc.github.io/tools/*</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -10396,12 +15496,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Directory Table</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Project Index</t>
+          <t>Dofollow CTA &amp; Directory Profile</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -10413,12 +15513,12 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Central Tools Hub</t>
+          <t>GitHub Pages Benchmark Hub</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/tools.html</t>
+          <t>jibranpcccc.github.io/benchmarks/*</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -10428,12 +15528,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Directory Hub</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Directory Hub</t>
+          <t>Dofollow Benchmark Architecture Hub</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -10445,12 +15545,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Machine API Feed</t>
+          <t>GitHub Raw CDN Documentation</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/api/v1/tools.json</t>
+          <t>raw.githubusercontent.com/.../README.md</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -10460,29 +15560,29 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Machine Registry</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>JSON Discovery Protocol</t>
+          <t>Direct Markdown API Endpoints</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Instant</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Tools XML Sitemap</t>
+          <t>GitHub Raw CDN Benchmark Specs</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/sitemap-tools.xml</t>
+          <t>raw.githubusercontent.com/.../BENCHMARKS.md</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -10492,79 +15592,271 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>XML Protocol</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Dedicated Sitemap Protocol</t>
+          <t>Direct Benchmark Markdown Specs</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Instant</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>PDF Technical Whitepapers</t>
+          <t>GitHub Profile Portfolio Showcase</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Edge Anycast CDNs</t>
+          <t>github.com/jibranpcccc</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>DA 95 Ready</t>
+          <t>DA 96</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>20 Links</t>
+          <t>Sitewide Hub</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Clickable Embedded Document Links</t>
+          <t>Dofollow Technical Portfolio</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>1–3 Days</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>GitHub Monorepo Index</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>github.com/.../digitalcreatoravi-seo-engine</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Directory Table</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Dofollow Monorepo README</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Pages Central Tools Hub</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/tools.html</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Directory Hub</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Dofollow Directory Hub</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Pages Root Landing Page</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Featured Card</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Sitewide Navigation Card</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Pages Machine API Feed</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/api/v1/tools.json</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Machine Registry</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>JSON Discovery Protocol</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Pages Tools XML Sitemap</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/sitemap-tools.xml</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>42 URLs</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Dedicated XML Sitemap Protocol</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>PDF Technical Whitepapers</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Edge Anycast CDNs</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>DA 95 Ready</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>20 Links</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Clickable Embedded Document Links</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>1–3 Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>RSS 2.0 XML Syndication Feeds</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Edge Anycast CDNs</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>DA 90</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>20 Channels</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>XML Auto-Discovery Protocol</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
@@ -10581,10 +15873,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -10608,7 +15900,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:17:43 UTC</t>
+          <t>2026-09-11 09:09:37 UTC</t>
         </is>
       </c>
     </row>
@@ -10631,7 +15923,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>166</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -10666,7 +15958,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>100.0% (166/166 Verified HTTP 200/202)</t>
+          <t>100.0% (266/266 Verified HTTP 200/202)</t>
         </is>
       </c>
     </row>
@@ -10678,7 +15970,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>594 ms</t>
+          <t>653 ms</t>
         </is>
       </c>
     </row>
@@ -10697,22 +15989,34 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>IndexNow Notification Status</t>
+          <t>Personal Email Quarantine Enforcement</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>20/20 Dispatched to Bing, Yandex, Seznam (100% Accepted)</t>
+          <t>100% Zero-Email Leaks (Dedicated Cluster Authentication)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>IndexNow Notification Status</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>20/20 Dispatched to Bing, Yandex, Seznam (100% Accepted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>Google Search Console Submissions</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>All 20 Properties Registered &amp; Active</t>
         </is>

--- a/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
+++ b/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K267"/>
+  <dimension ref="A1:K347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>938</v>
+        <v>1004</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1433</v>
+        <v>1083</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>376</v>
+        <v>290</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>376</v>
+        <v>458</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>365</v>
+        <v>299</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>879</v>
+        <v>1075</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>848</v>
+        <v>1161</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>933</v>
+        <v>892</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>877</v>
+        <v>796</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>918</v>
+        <v>838</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1021</v>
+        <v>778</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>940</v>
+        <v>853</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>786</v>
+        <v>886</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>930</v>
+        <v>843</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>931</v>
+        <v>817</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>878</v>
+        <v>916</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>869</v>
+        <v>1289</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>845</v>
+        <v>793</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>942</v>
+        <v>779</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>872</v>
+        <v>778</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>794</v>
+        <v>907</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>825</v>
+        <v>790</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>921</v>
+        <v>693</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>822</v>
+        <v>898</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>703</v>
+        <v>747</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>806</v>
+        <v>723</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>775</v>
+        <v>737</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>847</v>
+        <v>816</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>914</v>
+        <v>807</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>805</v>
+        <v>780</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>813</v>
+        <v>846</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>760</v>
+        <v>696</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>782</v>
+        <v>928</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>768</v>
+        <v>803</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>766</v>
+        <v>735</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>766</v>
+        <v>741</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>795</v>
+        <v>872</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>779</v>
+        <v>835</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1046</v>
+        <v>751</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>858</v>
+        <v>799</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1118</v>
+        <v>823</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>806</v>
+        <v>764</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>772</v>
+        <v>740</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>807</v>
+        <v>870</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>727</v>
+        <v>791</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>789</v>
+        <v>814</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>836</v>
+        <v>849</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>745</v>
+        <v>826</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>779</v>
+        <v>722</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>920</v>
+        <v>741</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>764</v>
+        <v>669</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>806</v>
+        <v>694</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>775</v>
+        <v>692</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>800</v>
+        <v>681</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>880</v>
+        <v>749</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>724</v>
+        <v>740</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>799</v>
+        <v>698</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>680</v>
+        <v>870</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>875</v>
+        <v>732</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>680</v>
+        <v>6872</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>691</v>
+        <v>732</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>772</v>
+        <v>1665</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>686</v>
+        <v>2779</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1367</v>
+        <v>275</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>252</v>
+        <v>590</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>269</v>
+        <v>383</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>897</v>
+        <v>441</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>429</v>
+        <v>472</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>389</v>
+        <v>571</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>411</v>
+        <v>1212</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>543</v>
+        <v>403</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>414</v>
+        <v>457</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>413</v>
+        <v>467</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>611</v>
+        <v>429</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2250</v>
+        <v>445</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1171</v>
+        <v>620</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>379</v>
+        <v>3313</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>221</v>
+        <v>96</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1221</v>
+        <v>1119</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>900</v>
+        <v>611</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1079</v>
+        <v>340</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>895</v>
+        <v>591</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>921</v>
+        <v>379</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>902</v>
+        <v>323</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>560</v>
+        <v>446</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>425</v>
+        <v>658</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>198</v>
+        <v>111</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1472</v>
+        <v>1236</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>932</v>
+        <v>663</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>548</v>
+        <v>437</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1271</v>
+        <v>975</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1023</v>
+        <v>322</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>358</v>
+        <v>266</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>743</v>
+        <v>985</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>868</v>
+        <v>302</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1151</v>
+        <v>536</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>867</v>
+        <v>317</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>596</v>
+        <v>276</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>563</v>
+        <v>302</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>638</v>
+        <v>537</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>809</v>
+        <v>729</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>803</v>
+        <v>265</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>556</v>
+        <v>347</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>889</v>
+        <v>738</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>821</v>
+        <v>694</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>655</v>
+        <v>866</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>772</v>
+        <v>686</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>698</v>
+        <v>620</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>801</v>
+        <v>650</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>642</v>
+        <v>605</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>698</v>
+        <v>1025</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>701</v>
+        <v>648</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>730</v>
+        <v>897</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>654</v>
+        <v>765</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>1751</v>
+        <v>692</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>722</v>
+        <v>665</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>660</v>
+        <v>861</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>677</v>
+        <v>639</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>705</v>
+        <v>638</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>761</v>
+        <v>817</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>768</v>
+        <v>826</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>786</v>
+        <v>835</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>748</v>
+        <v>850</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>812</v>
+        <v>778</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>926</v>
+        <v>837</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>761</v>
+        <v>718</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>817</v>
+        <v>870</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>771</v>
+        <v>737</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>778</v>
+        <v>703</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>886</v>
+        <v>1071</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>783</v>
+        <v>729</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>732</v>
+        <v>809</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>757</v>
+        <v>850</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>773</v>
+        <v>865</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>879</v>
+        <v>842</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>827</v>
+        <v>773</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>891</v>
+        <v>795</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>869</v>
+        <v>710</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>757</v>
+        <v>1834</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>733</v>
+        <v>831</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>843</v>
+        <v>735</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>802</v>
+        <v>914</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>783</v>
+        <v>972</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>783</v>
+        <v>738</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>852</v>
+        <v>822</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>790</v>
+        <v>764</v>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>386</v>
+        <v>317</v>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>367</v>
+        <v>281</v>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>396</v>
+        <v>287</v>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>393</v>
+        <v>272</v>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>381</v>
+        <v>298</v>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>426</v>
+        <v>323</v>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>348</v>
+        <v>423</v>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>375</v>
+        <v>443</v>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>368</v>
+        <v>499</v>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>342</v>
+        <v>436</v>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>353</v>
+        <v>423</v>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>788</v>
+        <v>477</v>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>346</v>
+        <v>484</v>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>369</v>
+        <v>566</v>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>371</v>
+        <v>492</v>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>340</v>
+        <v>502</v>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>408</v>
+        <v>565</v>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>367</v>
+        <v>530</v>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>343</v>
+        <v>558</v>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>330</v>
+        <v>542</v>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>503</v>
+        <v>418</v>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>351</v>
+        <v>790</v>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
@@ -14121,6 +14121,4086 @@
       <c r="K267" s="3" t="inlineStr">
         <is>
           <t>Empirical Benchmarks: EdgeRuntimeHQ (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="20" customHeight="1">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/local-agent-hardware-stack/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="J268" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: LocalAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="20" customHeight="1">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/workation-coliving-radar/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="J269" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: WorkationRadar</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/open-agent-protocol-hub/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="J270" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: OpenAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/indie-saas-stack-audit/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: IndieStackAudit</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/vector-database-benchmarks/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: VectorBench</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="20" customHeight="1">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/nomad-tax-treaty-calculator/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="n">
+        <v>511</v>
+      </c>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: NomadTreaty</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="20" customHeight="1">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/webhook-signature-audit/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="n">
+        <v>883</v>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K274" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: WebhookWatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="20" customHeight="1">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/local-pdf-privacy-redactor/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: LocalDocPrivacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/founder-runway-calculator/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="n">
+        <v>1524</v>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: FounderRunway</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="20" customHeight="1">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/rag-semantic-chunking-bench/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: RAGInspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="20" customHeight="1">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/nomad-passport-visa-index/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: NomadPassportIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="20" customHeight="1">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/saas-unit-economics-calculator/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="n">
+        <v>526</v>
+      </c>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: SaaSUnitMath</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="20" customHeight="1">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/nginx-grok-log-tester/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: GrokLogTester</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/soc2-readiness-checklist/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="n">
+        <v>484</v>
+      </c>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: SOC2Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="20" customHeight="1">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/global-eor-payroll-calculator/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="J282" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: EORCalculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="20" customHeight="1">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/devcontainer-docker-generator/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: DevConfigHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="20" customHeight="1">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/open-crm-migration-tco/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: OpenCRMStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="20" customHeight="1">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/github-actions-dag-validator/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: CIPipelineGraph</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="20" customHeight="1">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/options-greeks-visualizer/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: GreekVisualizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="20" customHeight="1">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/jibranpcccc/webgpu-edge-inference-bench/blob/main/benchmark_calculator.ipynb</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>Google Colab (DA 98)</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Run live in Google Colab: EdgeRuntimeHQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="20" customHeight="1">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/local-agent-hardware-stack/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="J288" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: LocalAgentStack (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="20" customHeight="1">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/workation-coliving-radar/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: WorkationRadar (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="20" customHeight="1">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/open-agent-protocol-hub/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="J290" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: OpenAgentStack (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="20" customHeight="1">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/indie-saas-stack-audit/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K291" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: IndieStackAudit (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="20" customHeight="1">
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/vector-database-benchmarks/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K292" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: VectorBench (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="20" customHeight="1">
+      <c r="A293" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/nomad-tax-treaty-calculator/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="n">
+        <v>522</v>
+      </c>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: NomadTreaty (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="20" customHeight="1">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/webhook-signature-audit/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="J294" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: WebhookWatch (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="20" customHeight="1">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/local-pdf-privacy-redactor/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: LocalDocPrivacy (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="20" customHeight="1">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/founder-runway-calculator/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: FounderRunway (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="20" customHeight="1">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/rag-semantic-chunking-bench/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: RAGInspect (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="20" customHeight="1">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/nomad-passport-visa-index/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="n">
+        <v>1296</v>
+      </c>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K298" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: NomadPassportIndex (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="20" customHeight="1">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/saas-unit-economics-calculator/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K299" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: SaaSUnitMath (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="20" customHeight="1">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/nginx-grok-log-tester/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="n">
+        <v>515</v>
+      </c>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: GrokLogTester (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="20" customHeight="1">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/soc2-readiness-checklist/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: SOC2Ready (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="20" customHeight="1">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/global-eor-payroll-calculator/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="n">
+        <v>1227</v>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K302" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: EORCalculator (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="20" customHeight="1">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/devcontainer-docker-generator/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: DevConfigHub (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="20" customHeight="1">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/open-crm-migration-tco/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: OpenCRMStack (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="20" customHeight="1">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/github-actions-dag-validator/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: CIPipelineGraph (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="20" customHeight="1">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/options-greeks-visualizer/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K306" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: GreekVisualizer (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="20" customHeight="1">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jibranpcccc/webgpu-edge-inference-bench/main/openapi.json</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Raw CDN OpenAPI (DA 96)</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI 3.1 Spec: EdgeRuntimeHQ (Raw CDN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="20" customHeight="1">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-1.json</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="J308" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K308" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: LocalAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="20" customHeight="1">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-10.json</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="J309" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: RAGInspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="20" customHeight="1">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-11.json</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="J310" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K310" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: NomadPassportIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="20" customHeight="1">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-12.json</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="J311" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: SaaSUnitMath</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="20" customHeight="1">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-13.json</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K312" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: GrokLogTester</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="20" customHeight="1">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-14.json</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="J313" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: SOC2Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="20" customHeight="1">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-15.json</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="J314" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: EORCalculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="20" customHeight="1">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-16.json</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="J315" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: DevConfigHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="20" customHeight="1">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-17.json</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="J316" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K316" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: OpenCRMStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="20" customHeight="1">
+      <c r="A317" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-18.json</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="J317" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: CIPipelineGraph</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="20" customHeight="1">
+      <c r="A318" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-19.json</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="J318" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: GreekVisualizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="20" customHeight="1">
+      <c r="A319" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-2.json</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="J319" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K319" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: WorkationRadar</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="20" customHeight="1">
+      <c r="A320" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-20.json</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="J320" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K320" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: EdgeRuntimeHQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="20" customHeight="1">
+      <c r="A321" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-3.json</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="J321" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K321" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: OpenAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="20" customHeight="1">
+      <c r="A322" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-4.json</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="J322" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K322" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: IndieStackAudit</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="20" customHeight="1">
+      <c r="A323" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-5.json</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="J323" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: VectorBench</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="20" customHeight="1">
+      <c r="A324" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-6.json</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="J324" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K324" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: NomadTreaty</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="20" customHeight="1">
+      <c r="A325" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-7.json</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K325" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: WebhookWatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="20" customHeight="1">
+      <c r="A326" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-8.json</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="J326" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K326" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: LocalDocPrivacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="20" customHeight="1">
+      <c r="A327" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/api/v1/site-9.json</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Pages API v1 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K327" s="3" t="inlineStr">
+        <is>
+          <t>API v1 Service Descriptor: FounderRunway</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="20" customHeight="1">
+      <c r="A328" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/40172eea9fbe12e07ca96d5567e8477b</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="J328" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K328" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: LocalAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="20" customHeight="1">
+      <c r="A329" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/101589b97f035ec7aa37ffbb84bd1310</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="J329" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K329" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: WorkationRadar</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="20" customHeight="1">
+      <c r="A330" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/4ebc8914729926e0c20a5a2b3674e947</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K330" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: OpenAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="20" customHeight="1">
+      <c r="A331" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/4184b6353527eb72a309f90ec252aa8e</t>
+        </is>
+      </c>
+      <c r="F331" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="J331" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K331" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: IndieStackAudit</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="20" customHeight="1">
+      <c r="A332" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/302850e404edafa69033dea5bf9127d2</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="n">
+        <v>635</v>
+      </c>
+      <c r="J332" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K332" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: VectorBench</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="20" customHeight="1">
+      <c r="A333" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/e480c996c9facab4de3f704682329c6c</t>
+        </is>
+      </c>
+      <c r="F333" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="n">
+        <v>677</v>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K333" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: NomadTreaty</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="20" customHeight="1">
+      <c r="A334" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/e9632cda454a3eab499ee90bebf30402</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="J334" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K334" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: WebhookWatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="20" customHeight="1">
+      <c r="A335" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/ced29a412d472aba9511364eea915217</t>
+        </is>
+      </c>
+      <c r="F335" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="J335" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K335" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: LocalDocPrivacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="20" customHeight="1">
+      <c r="A336" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/aa2490b5a17c9cc0d497633365ace6a0</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="n">
+        <v>647</v>
+      </c>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K336" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: FounderRunway</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="20" customHeight="1">
+      <c r="A337" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/23a6720e2ba03713a33dd372608f1389</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K337" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: RAGInspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="20" customHeight="1">
+      <c r="A338" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>site-11</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>NomadPassportIndex</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadpassportindex.netlify.app/</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/8403cbc7cd642f0abfcf1e29db2b1e0d</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="n">
+        <v>637</v>
+      </c>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K338" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: NomadPassportIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="20" customHeight="1">
+      <c r="A339" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>site-12</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>SaaSUnitMath</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>https://site-12-taupe.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/f9a48fa84fc715369a26538c8f77e811</t>
+        </is>
+      </c>
+      <c r="F339" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="J339" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K339" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: SaaSUnitMath</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="20" customHeight="1">
+      <c r="A340" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>site-13</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>GrokLogTester</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>https://groklogtester.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/9657bc4e8007677f5781bed496f1d728</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="n">
+        <v>956</v>
+      </c>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K340" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: GrokLogTester</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="20" customHeight="1">
+      <c r="A341" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>site-14</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>SOC2Ready</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>https://site-14-sable.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/6152f1c4655455aaa01dd6a80d24cb7a</t>
+        </is>
+      </c>
+      <c r="F341" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K341" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: SOC2Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="20" customHeight="1">
+      <c r="A342" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>site-15</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>EORCalculator</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>https://site-15-ruby.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/ff3634ef75e4c8a885dbac8587876189</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K342" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: EORCalculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="20" customHeight="1">
+      <c r="A343" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>site-16</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>DevConfigHub</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>https://site-16-indol.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/f4648aa100a20792e57127ed54fa429d</t>
+        </is>
+      </c>
+      <c r="F343" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="n">
+        <v>1621</v>
+      </c>
+      <c r="J343" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K343" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: DevConfigHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="20" customHeight="1">
+      <c r="A344" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>site-17</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>OpenCRMStack</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>https://opencrmstack.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/e6b44d8980b5fa76aba7e6fb0aeed059</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="J344" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K344" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: OpenCRMStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="20" customHeight="1">
+      <c r="A345" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>site-18</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>CIPipelineGraph</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>https://site-18-chi.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/fc172146ab589d04e2251964db1f35cb</t>
+        </is>
+      </c>
+      <c r="F345" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="J345" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K345" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: CIPipelineGraph</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="20" customHeight="1">
+      <c r="A346" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>site-19</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>GreekVisualizer</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>https://site-19-nine.vercel.app/</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/34860b2b00cf662ae660bf8444b7c792</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="n">
+        <v>759</v>
+      </c>
+      <c r="J346" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K346" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: GreekVisualizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="20" customHeight="1">
+      <c r="A347" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>site-20</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>EdgeRuntimeHQ</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>https://edgeruntimehq.pages.dev/</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/fbf6e35bf735a71f6784daa3e12157d1</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 3 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="n">
+        <v>793</v>
+      </c>
+      <c r="J347" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K347" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Architecture: EdgeRuntimeHQ</t>
         </is>
       </c>
     </row>
@@ -14135,22 +18215,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="63" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14171,50 +18254,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>DA 98 Colab</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>DA 96 Repos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>DA 96 Releases</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DA 96 Issues</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>DA 96 Gists</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DA 96 Pages</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>DA 96 Raw CDN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>DA 96 OpenAPI</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>DA 96 API Registry</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PDF Whitepapers</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>RSS Feeds</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Total Live Links</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Max Authority</t>
         </is>
@@ -14240,7 +18338,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>2</v>
@@ -14249,23 +18347,32 @@
         <v>2</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14289,7 +18396,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>2</v>
@@ -14298,23 +18405,32 @@
         <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O3" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14338,7 +18454,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>2</v>
@@ -14347,23 +18463,32 @@
         <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="L4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14387,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -14396,23 +18521,32 @@
         <v>2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O5" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14436,7 +18570,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>2</v>
@@ -14445,23 +18579,32 @@
         <v>2</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="L6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14485,7 +18628,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>2</v>
@@ -14494,23 +18637,32 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O7" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14534,7 +18686,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>2</v>
@@ -14543,23 +18695,32 @@
         <v>2</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="L8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14583,7 +18744,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>2</v>
@@ -14592,23 +18753,32 @@
         <v>2</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="L9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14632,7 +18802,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>2</v>
@@ -14641,23 +18811,32 @@
         <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14681,7 +18860,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>2</v>
@@ -14690,23 +18869,32 @@
         <v>2</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="L11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O11" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14730,7 +18918,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>2</v>
@@ -14739,23 +18927,32 @@
         <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="L12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14779,7 +18976,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>2</v>
@@ -14788,23 +18985,32 @@
         <v>2</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="L13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O13" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14828,7 +19034,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>2</v>
@@ -14837,23 +19043,32 @@
         <v>2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="L14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O14" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14877,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>2</v>
@@ -14886,23 +19101,32 @@
         <v>2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O15" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14926,7 +19150,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>2</v>
@@ -14935,23 +19159,32 @@
         <v>2</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="L16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -14975,7 +19208,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>2</v>
@@ -14984,23 +19217,32 @@
         <v>2</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="L17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -15024,7 +19266,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>2</v>
@@ -15033,23 +19275,32 @@
         <v>2</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="L18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -15073,7 +19324,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>2</v>
@@ -15082,23 +19333,32 @@
         <v>2</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -15122,7 +19382,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>2</v>
@@ -15131,23 +19391,32 @@
         <v>2</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -15171,7 +19440,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>2</v>
@@ -15180,23 +19449,32 @@
         <v>2</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="L21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>DA 96</t>
+      <c r="O21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>DA 98</t>
         </is>
       </c>
     </row>
@@ -15211,14 +19489,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -15257,17 +19535,17 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>GitHub Standalone Repositories</t>
+          <t>Google Colab Interactive Notebooks</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>github.com/jibranpcccc/*</t>
+          <t>colab.research.google.com/github/...</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>DA 96</t>
+          <t>DA 98</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -15277,24 +19555,24 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Homepage Metadata &amp; README</t>
+          <t>Runnable Cloud Notebook &amp; Interactive Math</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>24–48 Hours</t>
+          <t>Instant / 12 Hours</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>GitHub v1.0.0 Tagged Releases</t>
+          <t>GitHub Standalone Repositories</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../releases/tag/v1.0.0</t>
+          <t>github.com/jibranpcccc/*</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -15309,7 +19587,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Release Notes</t>
+          <t>Dofollow Homepage Metadata &amp; README</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -15321,12 +19599,12 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GitHub v1.1.0 Advanced Releases</t>
+          <t>GitHub v1.0.0 Tagged Releases</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../releases/tag/v1.1.0</t>
+          <t>github.com/.../releases/tag/v1.0.0</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -15341,7 +19619,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Empirical Benchmarks Release Notes</t>
+          <t>Dofollow Release Notes</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -15353,12 +19631,12 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>GitHub Official Issues #1 (Specs)</t>
+          <t>GitHub v1.1.0 Advanced Releases</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../issues/1</t>
+          <t>github.com/.../releases/tag/v1.1.0</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -15373,24 +19651,24 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Technical Tracker &amp; Specs</t>
+          <t>Empirical Benchmarks Release Notes</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>12–24 Hours</t>
+          <t>24–48 Hours</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GitHub Technical RFC Issues #2</t>
+          <t>GitHub Official Issues #1 (Specs)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../issues/2</t>
+          <t>github.com/.../issues/1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -15405,7 +19683,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Official Architecture RFC Specification</t>
+          <t>Dofollow Technical Tracker &amp; Specs</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -15417,12 +19695,12 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Public GitHub Gists (Wave 1)</t>
+          <t>GitHub Technical RFC Issues #2</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>gist.github.com/jibranpcccc/*</t>
+          <t>github.com/.../issues/2</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -15437,19 +19715,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Runnable Code Snippets</t>
+          <t>Official Architecture RFC Specification</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>24–48 Hours</t>
+          <t>12–24 Hours</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Public GitHub Gists (Wave 2)</t>
+          <t>Public GitHub Gists (Wave 1)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -15469,7 +19747,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Deep-Tech Runnable Guides &amp; Math</t>
+          <t>Dofollow Runnable Code Snippets</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -15481,12 +19759,12 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Tools Directory</t>
+          <t>Public GitHub Gists (Wave 2)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/tools/*</t>
+          <t>gist.github.com/jibranpcccc/*</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -15501,24 +19779,24 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Dofollow CTA &amp; Directory Profile</t>
+          <t>Deep-Tech Runnable Guides &amp; Math</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>24–48 Hours</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Benchmark Hub</t>
+          <t>Public GitHub Gists (Wave 3)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/benchmarks/*</t>
+          <t>gist.github.com/jibranpcccc/*</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -15533,24 +19811,24 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Benchmark Architecture Hub</t>
+          <t>Advanced Tech Guides &amp; Benchmark Scripts</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>24–48 Hours</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN Documentation</t>
+          <t>GitHub Pages Tools Directory</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>raw.githubusercontent.com/.../README.md</t>
+          <t>jibranpcccc.github.io/tools/*</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -15565,24 +19843,24 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Direct Markdown API Endpoints</t>
+          <t>Dofollow CTA &amp; Directory Profile</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GitHub Raw CDN Benchmark Specs</t>
+          <t>GitHub Pages Benchmark Hub</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>raw.githubusercontent.com/.../BENCHMARKS.md</t>
+          <t>jibranpcccc.github.io/benchmarks/*</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -15597,24 +19875,24 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Direct Benchmark Markdown Specs</t>
+          <t>Dofollow Benchmark Architecture Hub</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GitHub Profile Portfolio Showcase</t>
+          <t>GitHub Pages API v1 Service Registry</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>github.com/jibranpcccc</t>
+          <t>jibranpcccc.github.io/api/v1/*.json</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -15624,12 +19902,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Sitewide Hub</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Technical Portfolio</t>
+          <t>JSON Schema &amp; Machine Discovery</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -15641,12 +19919,12 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GitHub Monorepo Index</t>
+          <t>GitHub Raw CDN Documentation</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>github.com/.../digitalcreatoravi-seo-engine</t>
+          <t>raw.githubusercontent.com/.../README.md</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -15656,29 +19934,29 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Directory Table</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Monorepo README</t>
+          <t>Direct Markdown API Endpoints</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Instant</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Central Tools Hub</t>
+          <t>GitHub Raw CDN Benchmark Specs</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/tools.html</t>
+          <t>raw.githubusercontent.com/.../BENCHMARKS.md</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -15688,29 +19966,29 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Directory Hub</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Dofollow Directory Hub</t>
+          <t>Direct Benchmark Markdown Specs</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Instant</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Root Landing Page</t>
+          <t>GitHub Raw CDN OpenAPI 3.1 Specs</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/</t>
+          <t>raw.githubusercontent.com/.../openapi.json</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -15720,29 +19998,29 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Featured Card</t>
+          <t>20 Links</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Sitewide Navigation Card</t>
+          <t>OpenAPI 3.1 JSON Specification</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Instant</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Machine API Feed</t>
+          <t>GitHub Profile Portfolio Showcase</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/api/v1/tools.json</t>
+          <t>github.com/jibranpcccc</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -15752,29 +20030,29 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Machine Registry</t>
+          <t>Sitewide Hub</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>JSON Discovery Protocol</t>
+          <t>Dofollow Technical Portfolio</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GitHub Pages Tools XML Sitemap</t>
+          <t>GitHub Monorepo Index</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>jibranpcccc.github.io/sitemap-tools.xml</t>
+          <t>github.com/.../digitalcreatoravi-seo-engine</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -15784,79 +20062,207 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>42 URLs</t>
+          <t>Directory Table</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Dedicated XML Sitemap Protocol</t>
+          <t>Dofollow Monorepo README</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PDF Technical Whitepapers</t>
+          <t>GitHub Pages Central Tools Hub</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Edge Anycast CDNs</t>
+          <t>jibranpcccc.github.io/tools.html</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DA 95 Ready</t>
+          <t>DA 96</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>20 Links</t>
+          <t>Directory Hub</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Clickable Embedded Document Links</t>
+          <t>Dofollow Directory Hub</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1–3 Days</t>
+          <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>GitHub Pages Root Landing Page</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Featured Card</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Sitewide Navigation Card</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Pages Machine API Feed</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/api/v1/tools.json</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Machine Registry</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>JSON Discovery Protocol</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Pages Tools XML Sitemap</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>jibranpcccc.github.io/sitemap-tools.xml</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DA 96</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>42 URLs</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Dedicated XML Sitemap Protocol</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>PDF Technical Whitepapers</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Edge Anycast CDNs</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DA 95 Ready</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>20 Links</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Clickable Embedded Document Links</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>1–3 Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>RSS 2.0 XML Syndication Feeds</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Edge Anycast CDNs</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>DA 90</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>20 Channels</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>XML Auto-Discovery Protocol</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
@@ -15900,7 +20306,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:09:37 UTC</t>
+          <t>2026-09-11 11:12:47 UTC</t>
         </is>
       </c>
     </row>
@@ -15923,7 +20329,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>266</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -15946,7 +20352,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>GitHub (DA 96)</t>
+          <t>Google Colab (DA 98) &amp; GitHub (DA 96)</t>
         </is>
       </c>
     </row>
@@ -15958,7 +20364,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>100.0% (266/266 Verified HTTP 200/202)</t>
+          <t>100.0% (346/346 Verified HTTP 200/202)</t>
         </is>
       </c>
     </row>
@@ -15970,7 +20376,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>653 ms</t>
+          <t>644 ms</t>
         </is>
       </c>
     </row>

--- a/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
+++ b/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1004</v>
+        <v>879</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1083</v>
+        <v>1158</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>290</v>
+        <v>640</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>458</v>
+        <v>390</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>299</v>
+        <v>373</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1075</v>
+        <v>825</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>909</v>
+        <v>801</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1161</v>
+        <v>903</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>892</v>
+        <v>850</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>796</v>
+        <v>904</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>838</v>
+        <v>964</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>821</v>
+        <v>841</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>778</v>
+        <v>861</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>853</v>
+        <v>973</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>886</v>
+        <v>979</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>843</v>
+        <v>877</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>817</v>
+        <v>972</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>916</v>
+        <v>819</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>833</v>
+        <v>874</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>925</v>
+        <v>812</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1289</v>
+        <v>1054</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>793</v>
+        <v>954</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>907</v>
+        <v>856</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>785</v>
+        <v>720</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>790</v>
+        <v>742</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>693</v>
+        <v>776</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>898</v>
+        <v>817</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>747</v>
+        <v>963</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>723</v>
+        <v>775</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>748</v>
+        <v>904</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>737</v>
+        <v>773</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>807</v>
+        <v>931</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>846</v>
+        <v>814</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>696</v>
+        <v>759</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>928</v>
+        <v>786</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>741</v>
+        <v>757</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>872</v>
+        <v>786</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>752</v>
+        <v>782</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>835</v>
+        <v>797</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>751</v>
+        <v>724</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>799</v>
+        <v>767</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>823</v>
+        <v>757</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>870</v>
+        <v>780</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>814</v>
+        <v>732</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>849</v>
+        <v>796</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>775</v>
+        <v>738</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>753</v>
+        <v>722</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>722</v>
+        <v>1112</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>771</v>
+        <v>855</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>669</v>
+        <v>987</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>664</v>
+        <v>929</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>692</v>
+        <v>642</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>749</v>
+        <v>711</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>740</v>
+        <v>666</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>882</v>
+        <v>710</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>870</v>
+        <v>732</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>732</v>
+        <v>695</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>705</v>
+        <v>640</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6872</v>
+        <v>908</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>732</v>
+        <v>690</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>718</v>
+        <v>690</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>726</v>
+        <v>696</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1665</v>
+        <v>793</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>680</v>
+        <v>713</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2779</v>
+        <v>809</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>590</v>
+        <v>289</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>262</v>
+        <v>337</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>383</v>
+        <v>292</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>441</v>
+        <v>1902</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>438</v>
+        <v>397</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>472</v>
+        <v>514</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>571</v>
+        <v>510</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1212</v>
+        <v>1152</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>428</v>
+        <v>939</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>482</v>
+        <v>406</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>514</v>
+        <v>449</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>467</v>
+        <v>409</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>429</v>
+        <v>1225</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>620</v>
+        <v>409</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>454</v>
+        <v>414</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>3313</v>
+        <v>386</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1119</v>
+        <v>966</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>611</v>
+        <v>322</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>340</v>
+        <v>413</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>591</v>
+        <v>329</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>150</v>
+        <v>298</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>446</v>
+        <v>348</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>658</v>
+        <v>617</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>162</v>
+        <v>293</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>101</v>
+        <v>295</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1236</v>
+        <v>1273</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>663</v>
+        <v>300</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>437</v>
+        <v>339</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>975</v>
+        <v>1117</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>59</v>
+        <v>382</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>985</v>
+        <v>583</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>112</v>
+        <v>306</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>536</v>
+        <v>319</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>537</v>
+        <v>295</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>729</v>
+        <v>1077</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>694</v>
+        <v>302</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>743</v>
+        <v>659</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>866</v>
+        <v>658</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>653</v>
+        <v>721</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>620</v>
+        <v>765</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>650</v>
+        <v>704</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>605</v>
+        <v>669</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>1025</v>
+        <v>685</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>897</v>
+        <v>646</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>710</v>
+        <v>641</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>628</v>
+        <v>661</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>861</v>
+        <v>639</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>647</v>
+        <v>681</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>826</v>
+        <v>717</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>835</v>
+        <v>740</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>850</v>
+        <v>741</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>778</v>
+        <v>884</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>859</v>
+        <v>811</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>837</v>
+        <v>787</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>718</v>
+        <v>889</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>756</v>
+        <v>780</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>807</v>
+        <v>775</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>870</v>
+        <v>771</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>905</v>
+        <v>759</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>737</v>
+        <v>860</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>703</v>
+        <v>794</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>1071</v>
+        <v>923</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>729</v>
+        <v>791</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>809</v>
+        <v>720</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>850</v>
+        <v>778</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>865</v>
+        <v>794</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>788</v>
+        <v>844</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>842</v>
+        <v>773</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>773</v>
+        <v>742</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>795</v>
+        <v>765</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>710</v>
+        <v>803</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>743</v>
+        <v>761</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>867</v>
+        <v>724</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>1834</v>
+        <v>846</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>914</v>
+        <v>774</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>972</v>
+        <v>849</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>738</v>
+        <v>841</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>822</v>
+        <v>799</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>330</v>
+        <v>287</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>323</v>
+        <v>630</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>287</v>
+        <v>389</v>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>360</v>
+        <v>299</v>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>428</v>
+        <v>277</v>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>474</v>
+        <v>283</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>423</v>
+        <v>1049</v>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>436</v>
+        <v>568</v>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>484</v>
+        <v>435</v>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>566</v>
+        <v>589</v>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>516</v>
+        <v>447</v>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>492</v>
+        <v>387</v>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>502</v>
+        <v>428</v>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>565</v>
+        <v>910</v>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>530</v>
+        <v>418</v>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>558</v>
+        <v>442</v>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>542</v>
+        <v>1015</v>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>790</v>
+        <v>398</v>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>1528</v>
+        <v>440</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>511</v>
+        <v>458</v>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>883</v>
+        <v>416</v>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>1524</v>
+        <v>446</v>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>480</v>
+        <v>1463</v>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>526</v>
+        <v>452</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>1441</v>
+        <v>416</v>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>438</v>
+        <v>1438</v>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>749</v>
+        <v>1157</v>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>599</v>
+        <v>516</v>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>524</v>
+        <v>433</v>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>492</v>
+        <v>433</v>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>1296</v>
+        <v>432</v>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>558</v>
+        <v>417</v>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>515</v>
+        <v>448</v>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>516</v>
+        <v>418</v>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="I302" s="2" t="n">
-        <v>1227</v>
+        <v>509</v>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="I303" s="2" t="n">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="I304" s="2" t="n">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="I305" s="2" t="n">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="I306" s="2" t="n">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="I307" s="2" t="n">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         </is>
       </c>
       <c r="I308" s="2" t="n">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="I309" s="2" t="n">
-        <v>368</v>
+        <v>289</v>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="I310" s="2" t="n">
-        <v>394</v>
+        <v>289</v>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="I311" s="2" t="n">
-        <v>378</v>
+        <v>303</v>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         </is>
       </c>
       <c r="I312" s="2" t="n">
-        <v>379</v>
+        <v>318</v>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="I313" s="2" t="n">
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="I314" s="2" t="n">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="I315" s="2" t="n">
-        <v>399</v>
+        <v>304</v>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="I316" s="2" t="n">
-        <v>399</v>
+        <v>313</v>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="I317" s="2" t="n">
-        <v>421</v>
+        <v>311</v>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="I318" s="2" t="n">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         </is>
       </c>
       <c r="I319" s="2" t="n">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="I320" s="2" t="n">
-        <v>407</v>
+        <v>336</v>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         </is>
       </c>
       <c r="I321" s="2" t="n">
-        <v>378</v>
+        <v>293</v>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="I322" s="2" t="n">
-        <v>367</v>
+        <v>272</v>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="I323" s="2" t="n">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="I324" s="2" t="n">
-        <v>446</v>
+        <v>272</v>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="I325" s="2" t="n">
-        <v>401</v>
+        <v>292</v>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="I326" s="2" t="n">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="I327" s="2" t="n">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="I328" s="2" t="n">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="I329" s="2" t="n">
-        <v>850</v>
+        <v>673</v>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         </is>
       </c>
       <c r="I330" s="2" t="n">
-        <v>741</v>
+        <v>638</v>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         </is>
       </c>
       <c r="I331" s="2" t="n">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="I332" s="2" t="n">
-        <v>635</v>
+        <v>661</v>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         </is>
       </c>
       <c r="I333" s="2" t="n">
-        <v>677</v>
+        <v>731</v>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="I334" s="2" t="n">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         </is>
       </c>
       <c r="I335" s="2" t="n">
-        <v>740</v>
+        <v>691</v>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         </is>
       </c>
       <c r="I336" s="2" t="n">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="I337" s="2" t="n">
-        <v>610</v>
+        <v>799</v>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         </is>
       </c>
       <c r="I338" s="2" t="n">
-        <v>637</v>
+        <v>732</v>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="I339" s="2" t="n">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="I340" s="2" t="n">
-        <v>956</v>
+        <v>664</v>
       </c>
       <c r="J340" s="4" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="I341" s="2" t="n">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="J341" s="4" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="I342" s="2" t="n">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         </is>
       </c>
       <c r="I343" s="2" t="n">
-        <v>1621</v>
+        <v>713</v>
       </c>
       <c r="J343" s="4" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         </is>
       </c>
       <c r="I344" s="2" t="n">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="I345" s="2" t="n">
-        <v>671</v>
+        <v>796</v>
       </c>
       <c r="J345" s="4" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         </is>
       </c>
       <c r="I346" s="2" t="n">
-        <v>759</v>
+        <v>653</v>
       </c>
       <c r="J346" s="4" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         </is>
       </c>
       <c r="I347" s="2" t="n">
-        <v>793</v>
+        <v>755</v>
       </c>
       <c r="J347" s="4" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 11:12:47 UTC</t>
+          <t>2026-09-11 12:50:09 UTC</t>
         </is>
       </c>
     </row>
@@ -20376,7 +20376,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>644 ms</t>
+          <t>597 ms</t>
         </is>
       </c>
     </row>

--- a/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
+++ b/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
@@ -485,13 +485,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K487"/>
+  <dimension ref="A1:K497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="63" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>968</v>
+        <v>935</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>271</v>
+        <v>357</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>257</v>
+        <v>421</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>264</v>
+        <v>419</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>999</v>
+        <v>884</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>897</v>
+        <v>833</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>884</v>
+        <v>982</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>896</v>
+        <v>835</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>874</v>
+        <v>1269</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>861</v>
+        <v>900</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>891</v>
+        <v>990</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>776</v>
+        <v>859</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>986</v>
+        <v>956</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>899</v>
+        <v>834</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>868</v>
+        <v>808</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>922</v>
+        <v>819</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>844</v>
+        <v>957</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>795</v>
+        <v>935</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>925</v>
+        <v>829</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>885</v>
+        <v>979</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>830</v>
+        <v>1134</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>836</v>
+        <v>886</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>817</v>
+        <v>896</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>848</v>
+        <v>874</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1225</v>
+        <v>940</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1074</v>
+        <v>901</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>986</v>
+        <v>947</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>770</v>
+        <v>836</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>758</v>
+        <v>784</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>730</v>
+        <v>748</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>745</v>
+        <v>863</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>955</v>
+        <v>820</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>759</v>
+        <v>783</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>742</v>
+        <v>834</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>802</v>
+        <v>732</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>809</v>
+        <v>737</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>874</v>
+        <v>741</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>739</v>
+        <v>755</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>772</v>
+        <v>820</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>836</v>
+        <v>760</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>838</v>
+        <v>747</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>763</v>
+        <v>724</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>768</v>
+        <v>714</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>811</v>
+        <v>707</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>783</v>
+        <v>744</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>720</v>
+        <v>809</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>729</v>
+        <v>818</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>756</v>
+        <v>728</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>766</v>
+        <v>730</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>791</v>
+        <v>712</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>745</v>
+        <v>785</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>844</v>
+        <v>717</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>799</v>
+        <v>838</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>845</v>
+        <v>726</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>789</v>
+        <v>734</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>827</v>
+        <v>696</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>824</v>
+        <v>736</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>770</v>
+        <v>694</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>825</v>
+        <v>782</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>867</v>
+        <v>743</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>727</v>
+        <v>757</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>763</v>
+        <v>935</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>801</v>
+        <v>747</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>728</v>
+        <v>825</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>793</v>
+        <v>727</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>780</v>
+        <v>698</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>811</v>
+        <v>726</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>720</v>
+        <v>874</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>609</v>
+        <v>847</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>993</v>
+        <v>784</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>608</v>
+        <v>832</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>613</v>
+        <v>753</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>761</v>
+        <v>666</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>701</v>
+        <v>737</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>605</v>
+        <v>752</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>650</v>
+        <v>729</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>682</v>
+        <v>720</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>636</v>
+        <v>601</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1235</v>
+        <v>685</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>417</v>
+        <v>1101</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>381</v>
+        <v>444</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>380</v>
+        <v>528</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>407</v>
+        <v>453</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>455</v>
+        <v>422</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>580</v>
+        <v>414</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>456</v>
+        <v>516</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>677</v>
+        <v>466</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>468</v>
+        <v>542</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>523</v>
+        <v>415</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>425</v>
+        <v>2011</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>436</v>
+        <v>494</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>521</v>
+        <v>413</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>462</v>
+        <v>432</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>1076</v>
+        <v>1134</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>305</v>
+        <v>406</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>318</v>
+        <v>597</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>292</v>
+        <v>409</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>327</v>
+        <v>679</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>331</v>
+        <v>569</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>420</v>
+        <v>517</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>1183</v>
+        <v>1083</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>369</v>
+        <v>273</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>1175</v>
+        <v>1134</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>372</v>
+        <v>296</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>740</v>
+        <v>573</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>325</v>
+        <v>280</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>450</v>
+        <v>377</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>426</v>
+        <v>352</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>593</v>
+        <v>378</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>446</v>
+        <v>338</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>533</v>
+        <v>396</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>904</v>
+        <v>350</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>429</v>
+        <v>374</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>463</v>
+        <v>389</v>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>848</v>
+        <v>344</v>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>264</v>
+        <v>567</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>284</v>
+        <v>567</v>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>732</v>
+        <v>868</v>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>796</v>
+        <v>707</v>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>659</v>
+        <v>753</v>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>758</v>
+        <v>939</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>668</v>
+        <v>747</v>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>751</v>
+        <v>721</v>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>721</v>
+        <v>965</v>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>610</v>
+        <v>668</v>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>754</v>
+        <v>649</v>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>732</v>
+        <v>649</v>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>813</v>
+        <v>673</v>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>710</v>
+        <v>661</v>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>701</v>
+        <v>609</v>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>608</v>
+        <v>699</v>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>765</v>
+        <v>668</v>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>643</v>
+        <v>1025</v>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>722</v>
+        <v>869</v>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>732</v>
+        <v>784</v>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>712</v>
+        <v>792</v>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>706</v>
+        <v>816</v>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>701</v>
+        <v>778</v>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>724</v>
+        <v>762</v>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>761</v>
+        <v>774</v>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>788</v>
+        <v>724</v>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>842</v>
+        <v>882</v>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>714</v>
+        <v>777</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>716</v>
+        <v>761</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>741</v>
+        <v>849</v>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>794</v>
+        <v>735</v>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>818</v>
+        <v>744</v>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>686</v>
+        <v>957</v>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>707</v>
+        <v>948</v>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>716</v>
+        <v>818</v>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>841</v>
+        <v>815</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>700</v>
+        <v>745</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>772</v>
+        <v>728</v>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="n">
-        <v>748</v>
+        <v>711</v>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>796</v>
+        <v>761</v>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>745</v>
+        <v>713</v>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>841</v>
+        <v>762</v>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>744</v>
+        <v>711</v>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>780</v>
+        <v>706</v>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>817</v>
+        <v>724</v>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>772</v>
+        <v>721</v>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>781</v>
+        <v>704</v>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>709</v>
+        <v>757</v>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>791</v>
+        <v>843</v>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>832</v>
+        <v>1143</v>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>785</v>
+        <v>737</v>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="I302" s="2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="I303" s="2" t="n">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="I304" s="2" t="n">
-        <v>749</v>
+        <v>777</v>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="I305" s="2" t="n">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="I306" s="2" t="n">
-        <v>731</v>
+        <v>693</v>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="I307" s="2" t="n">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         </is>
       </c>
       <c r="I308" s="2" t="n">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="I309" s="2" t="n">
-        <v>769</v>
+        <v>734</v>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="I310" s="2" t="n">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="I311" s="2" t="n">
-        <v>802</v>
+        <v>715</v>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         </is>
       </c>
       <c r="I312" s="2" t="n">
-        <v>777</v>
+        <v>729</v>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="I313" s="2" t="n">
-        <v>854</v>
+        <v>700</v>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="I314" s="2" t="n">
-        <v>783</v>
+        <v>736</v>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="I315" s="2" t="n">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="I316" s="2" t="n">
-        <v>755</v>
+        <v>725</v>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="I317" s="2" t="n">
-        <v>801</v>
+        <v>720</v>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="I318" s="2" t="n">
-        <v>392</v>
+        <v>263</v>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         </is>
       </c>
       <c r="I319" s="2" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="I320" s="2" t="n">
-        <v>392</v>
+        <v>302</v>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         </is>
       </c>
       <c r="I321" s="2" t="n">
-        <v>399</v>
+        <v>276</v>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="I322" s="2" t="n">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="I323" s="2" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="I324" s="2" t="n">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="I325" s="2" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="I326" s="2" t="n">
-        <v>371</v>
+        <v>258</v>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="I327" s="2" t="n">
-        <v>365</v>
+        <v>266</v>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="I328" s="2" t="n">
-        <v>356</v>
+        <v>278</v>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="I329" s="2" t="n">
-        <v>387</v>
+        <v>282</v>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         </is>
       </c>
       <c r="I330" s="2" t="n">
-        <v>372</v>
+        <v>267</v>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         </is>
       </c>
       <c r="I331" s="2" t="n">
-        <v>379</v>
+        <v>255</v>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="I332" s="2" t="n">
-        <v>376</v>
+        <v>264</v>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         </is>
       </c>
       <c r="I333" s="2" t="n">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="I334" s="2" t="n">
-        <v>383</v>
+        <v>254</v>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         </is>
       </c>
       <c r="I335" s="2" t="n">
-        <v>367</v>
+        <v>272</v>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         </is>
       </c>
       <c r="I336" s="2" t="n">
-        <v>373</v>
+        <v>264</v>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="I337" s="2" t="n">
-        <v>367</v>
+        <v>258</v>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         </is>
       </c>
       <c r="I338" s="2" t="n">
-        <v>401</v>
+        <v>272</v>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="I339" s="2" t="n">
-        <v>370</v>
+        <v>253</v>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="I340" s="2" t="n">
-        <v>385</v>
+        <v>277</v>
       </c>
       <c r="J340" s="4" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="I341" s="2" t="n">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="J341" s="4" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="I342" s="2" t="n">
-        <v>374</v>
+        <v>290</v>
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         </is>
       </c>
       <c r="I343" s="2" t="n">
-        <v>362</v>
+        <v>247</v>
       </c>
       <c r="J343" s="4" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         </is>
       </c>
       <c r="I344" s="2" t="n">
-        <v>391</v>
+        <v>265</v>
       </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="I345" s="2" t="n">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="J345" s="4" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         </is>
       </c>
       <c r="I346" s="2" t="n">
-        <v>371</v>
+        <v>280</v>
       </c>
       <c r="J346" s="4" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         </is>
       </c>
       <c r="I347" s="2" t="n">
-        <v>353</v>
+        <v>285</v>
       </c>
       <c r="J347" s="4" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         </is>
       </c>
       <c r="I348" s="2" t="n">
-        <v>468</v>
+        <v>848</v>
       </c>
       <c r="J348" s="4" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="I349" s="2" t="n">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="J349" s="4" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="I350" s="2" t="n">
-        <v>411</v>
+        <v>339</v>
       </c>
       <c r="J350" s="4" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="I351" s="2" t="n">
-        <v>424</v>
+        <v>362</v>
       </c>
       <c r="J351" s="4" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="I352" s="2" t="n">
-        <v>418</v>
+        <v>357</v>
       </c>
       <c r="J352" s="4" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="I353" s="2" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J353" s="4" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         </is>
       </c>
       <c r="I354" s="2" t="n">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="J354" s="4" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="I355" s="2" t="n">
-        <v>384</v>
+        <v>994</v>
       </c>
       <c r="J355" s="4" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="I356" s="2" t="n">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="J356" s="4" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="I357" s="2" t="n">
-        <v>477</v>
+        <v>378</v>
       </c>
       <c r="J357" s="4" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I358" s="2" t="n">
-        <v>383</v>
+        <v>1291</v>
       </c>
       <c r="J358" s="4" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="I359" s="2" t="n">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="J359" s="4" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="I360" s="2" t="n">
-        <v>398</v>
+        <v>557</v>
       </c>
       <c r="J360" s="4" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         </is>
       </c>
       <c r="I361" s="2" t="n">
-        <v>501</v>
+        <v>426</v>
       </c>
       <c r="J361" s="4" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         </is>
       </c>
       <c r="I362" s="2" t="n">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="J362" s="4" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         </is>
       </c>
       <c r="I363" s="2" t="n">
-        <v>404</v>
+        <v>817</v>
       </c>
       <c r="J363" s="4" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         </is>
       </c>
       <c r="I364" s="2" t="n">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="J364" s="4" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="I365" s="2" t="n">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="J365" s="4" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="I366" s="2" t="n">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="J366" s="4" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="I367" s="2" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J367" s="4" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         </is>
       </c>
       <c r="I368" s="2" t="n">
-        <v>408</v>
+        <v>858</v>
       </c>
       <c r="J368" s="4" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         </is>
       </c>
       <c r="I369" s="2" t="n">
-        <v>422</v>
+        <v>465</v>
       </c>
       <c r="J369" s="4" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="I370" s="2" t="n">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="J370" s="4" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         </is>
       </c>
       <c r="I371" s="2" t="n">
-        <v>1104</v>
+        <v>567</v>
       </c>
       <c r="J371" s="4" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         </is>
       </c>
       <c r="I372" s="2" t="n">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="J372" s="4" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="I373" s="2" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="J373" s="4" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="I374" s="2" t="n">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J374" s="4" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         </is>
       </c>
       <c r="I375" s="2" t="n">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="J375" s="4" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="I376" s="2" t="n">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="J376" s="4" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="I377" s="2" t="n">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="J377" s="4" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         </is>
       </c>
       <c r="I378" s="2" t="n">
-        <v>458</v>
+        <v>1531</v>
       </c>
       <c r="J378" s="4" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="I379" s="2" t="n">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="J379" s="4" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         </is>
       </c>
       <c r="I380" s="2" t="n">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="J380" s="4" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         </is>
       </c>
       <c r="I381" s="2" t="n">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="J381" s="4" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         </is>
       </c>
       <c r="I382" s="2" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="J382" s="4" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="I383" s="2" t="n">
-        <v>1441</v>
+        <v>437</v>
       </c>
       <c r="J383" s="4" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="I384" s="2" t="n">
-        <v>1444</v>
+        <v>430</v>
       </c>
       <c r="J384" s="4" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         </is>
       </c>
       <c r="I385" s="2" t="n">
-        <v>499</v>
+        <v>1416</v>
       </c>
       <c r="J385" s="4" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         </is>
       </c>
       <c r="I386" s="2" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="J386" s="4" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         </is>
       </c>
       <c r="I387" s="2" t="n">
-        <v>1521</v>
+        <v>1492</v>
       </c>
       <c r="J387" s="4" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         </is>
       </c>
       <c r="I388" s="2" t="n">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="J388" s="4" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="I389" s="2" t="n">
-        <v>485</v>
+        <v>422</v>
       </c>
       <c r="J389" s="4" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         </is>
       </c>
       <c r="I390" s="2" t="n">
-        <v>1492</v>
+        <v>416</v>
       </c>
       <c r="J390" s="4" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         </is>
       </c>
       <c r="I391" s="2" t="n">
-        <v>1517</v>
+        <v>412</v>
       </c>
       <c r="J391" s="4" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="I392" s="2" t="n">
-        <v>1510</v>
+        <v>1499</v>
       </c>
       <c r="J392" s="4" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="I393" s="2" t="n">
-        <v>1508</v>
+        <v>1481</v>
       </c>
       <c r="J393" s="4" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         </is>
       </c>
       <c r="I394" s="2" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J394" s="4" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         </is>
       </c>
       <c r="I395" s="2" t="n">
-        <v>430</v>
+        <v>1425</v>
       </c>
       <c r="J395" s="4" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         </is>
       </c>
       <c r="I396" s="2" t="n">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="J396" s="4" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         </is>
       </c>
       <c r="I397" s="2" t="n">
-        <v>1497</v>
+        <v>420</v>
       </c>
       <c r="J397" s="4" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="I398" s="2" t="n">
-        <v>456</v>
+        <v>1470</v>
       </c>
       <c r="J398" s="4" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         </is>
       </c>
       <c r="I399" s="2" t="n">
-        <v>429</v>
+        <v>1445</v>
       </c>
       <c r="J399" s="4" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         </is>
       </c>
       <c r="I400" s="2" t="n">
-        <v>427</v>
+        <v>1499</v>
       </c>
       <c r="J400" s="4" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="I401" s="2" t="n">
-        <v>1435</v>
+        <v>1421</v>
       </c>
       <c r="J401" s="4" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         </is>
       </c>
       <c r="I402" s="2" t="n">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="J402" s="4" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         </is>
       </c>
       <c r="I403" s="2" t="n">
-        <v>464</v>
+        <v>1446</v>
       </c>
       <c r="J403" s="4" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="I404" s="2" t="n">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="J404" s="4" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="I405" s="2" t="n">
-        <v>1500</v>
+        <v>455</v>
       </c>
       <c r="J405" s="4" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="I406" s="2" t="n">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="J406" s="4" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         </is>
       </c>
       <c r="I407" s="2" t="n">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="J407" s="4" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         </is>
       </c>
       <c r="I408" s="2" t="n">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="J408" s="4" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         </is>
       </c>
       <c r="I409" s="2" t="n">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="J409" s="4" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         </is>
       </c>
       <c r="I410" s="2" t="n">
-        <v>415</v>
+        <v>550</v>
       </c>
       <c r="J410" s="4" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         </is>
       </c>
       <c r="I411" s="2" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J411" s="4" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         </is>
       </c>
       <c r="I412" s="2" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J412" s="4" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="I413" s="2" t="n">
-        <v>411</v>
+        <v>547</v>
       </c>
       <c r="J413" s="4" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         </is>
       </c>
       <c r="I414" s="2" t="n">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="J414" s="4" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         </is>
       </c>
       <c r="I415" s="2" t="n">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="J415" s="4" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         </is>
       </c>
       <c r="I416" s="2" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="J416" s="4" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="I417" s="2" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="J417" s="4" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         </is>
       </c>
       <c r="I418" s="2" t="n">
-        <v>385</v>
+        <v>433</v>
       </c>
       <c r="J418" s="4" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         </is>
       </c>
       <c r="I419" s="2" t="n">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="J419" s="4" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         </is>
       </c>
       <c r="I420" s="2" t="n">
-        <v>390</v>
+        <v>554</v>
       </c>
       <c r="J420" s="4" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         </is>
       </c>
       <c r="I421" s="2" t="n">
-        <v>481</v>
+        <v>402</v>
       </c>
       <c r="J421" s="4" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         </is>
       </c>
       <c r="I422" s="2" t="n">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="J422" s="4" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         </is>
       </c>
       <c r="I423" s="2" t="n">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="J423" s="4" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         </is>
       </c>
       <c r="I424" s="2" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="J424" s="4" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         </is>
       </c>
       <c r="I425" s="2" t="n">
-        <v>405</v>
+        <v>516</v>
       </c>
       <c r="J425" s="4" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="I426" s="2" t="n">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="J426" s="4" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="I427" s="2" t="n">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="J427" s="4" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         </is>
       </c>
       <c r="I428" s="2" t="n">
-        <v>408</v>
+        <v>513</v>
       </c>
       <c r="J428" s="4" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         </is>
       </c>
       <c r="I429" s="2" t="n">
-        <v>561</v>
+        <v>396</v>
       </c>
       <c r="J429" s="4" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         </is>
       </c>
       <c r="I430" s="2" t="n">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="J430" s="4" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         </is>
       </c>
       <c r="I431" s="2" t="n">
-        <v>405</v>
+        <v>502</v>
       </c>
       <c r="J431" s="4" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         </is>
       </c>
       <c r="I432" s="2" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="J432" s="4" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="I433" s="2" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J433" s="4" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="I434" s="2" t="n">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="J434" s="4" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         </is>
       </c>
       <c r="I435" s="2" t="n">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="J435" s="4" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         </is>
       </c>
       <c r="I436" s="2" t="n">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="J436" s="4" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I437" s="2" t="n">
-        <v>417</v>
+        <v>741</v>
       </c>
       <c r="J437" s="4" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         </is>
       </c>
       <c r="I438" s="2" t="n">
-        <v>364</v>
+        <v>275</v>
       </c>
       <c r="J438" s="4" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         </is>
       </c>
       <c r="I439" s="2" t="n">
-        <v>1075</v>
+        <v>274</v>
       </c>
       <c r="J439" s="4" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         </is>
       </c>
       <c r="I440" s="2" t="n">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="J440" s="4" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         </is>
       </c>
       <c r="I441" s="2" t="n">
-        <v>371</v>
+        <v>290</v>
       </c>
       <c r="J441" s="4" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="I442" s="2" t="n">
-        <v>421</v>
+        <v>285</v>
       </c>
       <c r="J442" s="4" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         </is>
       </c>
       <c r="I443" s="2" t="n">
-        <v>374</v>
+        <v>254</v>
       </c>
       <c r="J443" s="4" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="I444" s="2" t="n">
-        <v>402</v>
+        <v>265</v>
       </c>
       <c r="J444" s="4" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         </is>
       </c>
       <c r="I445" s="2" t="n">
-        <v>369</v>
+        <v>268</v>
       </c>
       <c r="J445" s="4" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         </is>
       </c>
       <c r="I446" s="2" t="n">
-        <v>358</v>
+        <v>265</v>
       </c>
       <c r="J446" s="4" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         </is>
       </c>
       <c r="I447" s="2" t="n">
-        <v>379</v>
+        <v>290</v>
       </c>
       <c r="J447" s="4" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         </is>
       </c>
       <c r="I448" s="2" t="n">
-        <v>374</v>
+        <v>281</v>
       </c>
       <c r="J448" s="4" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         </is>
       </c>
       <c r="I449" s="2" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="J449" s="4" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="I450" s="2" t="n">
-        <v>371</v>
+        <v>280</v>
       </c>
       <c r="J450" s="4" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         </is>
       </c>
       <c r="I451" s="2" t="n">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="J451" s="4" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         </is>
       </c>
       <c r="I452" s="2" t="n">
-        <v>366</v>
+        <v>275</v>
       </c>
       <c r="J452" s="4" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         </is>
       </c>
       <c r="I453" s="2" t="n">
-        <v>379</v>
+        <v>260</v>
       </c>
       <c r="J453" s="4" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="I454" s="2" t="n">
-        <v>376</v>
+        <v>257</v>
       </c>
       <c r="J454" s="4" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         </is>
       </c>
       <c r="I455" s="2" t="n">
-        <v>383</v>
+        <v>267</v>
       </c>
       <c r="J455" s="4" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         </is>
       </c>
       <c r="I456" s="2" t="n">
-        <v>367</v>
+        <v>245</v>
       </c>
       <c r="J456" s="4" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         </is>
       </c>
       <c r="I457" s="2" t="n">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="J457" s="4" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         </is>
       </c>
       <c r="I458" s="2" t="n">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="J458" s="4" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         </is>
       </c>
       <c r="I459" s="2" t="n">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="J459" s="4" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         </is>
       </c>
       <c r="I460" s="2" t="n">
-        <v>374</v>
+        <v>255</v>
       </c>
       <c r="J460" s="4" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         </is>
       </c>
       <c r="I461" s="2" t="n">
-        <v>358</v>
+        <v>423</v>
       </c>
       <c r="J461" s="4" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         </is>
       </c>
       <c r="I462" s="2" t="n">
-        <v>396</v>
+        <v>279</v>
       </c>
       <c r="J462" s="4" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="I463" s="2" t="n">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="J463" s="4" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="I464" s="2" t="n">
-        <v>374</v>
+        <v>255</v>
       </c>
       <c r="J464" s="4" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         </is>
       </c>
       <c r="I465" s="2" t="n">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="J465" s="4" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="I466" s="2" t="n">
-        <v>381</v>
+        <v>269</v>
       </c>
       <c r="J466" s="4" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="I467" s="2" t="n">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="J467" s="4" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="I468" s="2" t="n">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="J468" s="4" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         </is>
       </c>
       <c r="I469" s="2" t="n">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="J469" s="4" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         </is>
       </c>
       <c r="I470" s="2" t="n">
-        <v>759</v>
+        <v>1001</v>
       </c>
       <c r="J470" s="4" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         </is>
       </c>
       <c r="I471" s="2" t="n">
-        <v>665</v>
+        <v>753</v>
       </c>
       <c r="J471" s="4" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="I472" s="2" t="n">
-        <v>780</v>
+        <v>663</v>
       </c>
       <c r="J472" s="4" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         </is>
       </c>
       <c r="I473" s="2" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="J473" s="4" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="I474" s="2" t="n">
-        <v>708</v>
+        <v>673</v>
       </c>
       <c r="J474" s="4" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="I475" s="2" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="J475" s="4" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         </is>
       </c>
       <c r="I476" s="2" t="n">
-        <v>666</v>
+        <v>746</v>
       </c>
       <c r="J476" s="4" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="I477" s="2" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J477" s="4" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         </is>
       </c>
       <c r="I478" s="2" t="n">
-        <v>652</v>
+        <v>633</v>
       </c>
       <c r="J478" s="4" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         </is>
       </c>
       <c r="I479" s="2" t="n">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="J479" s="4" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="I480" s="2" t="n">
-        <v>604</v>
+        <v>706</v>
       </c>
       <c r="J480" s="4" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="I481" s="2" t="n">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="J481" s="4" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="I482" s="2" t="n">
-        <v>683</v>
+        <v>736</v>
       </c>
       <c r="J482" s="4" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         </is>
       </c>
       <c r="I483" s="2" t="n">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="J483" s="4" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         </is>
       </c>
       <c r="I484" s="2" t="n">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="J484" s="4" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         </is>
       </c>
       <c r="I485" s="2" t="n">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="J485" s="4" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         </is>
       </c>
       <c r="I486" s="2" t="n">
-        <v>660</v>
+        <v>638</v>
       </c>
       <c r="J486" s="4" t="inlineStr">
         <is>
@@ -25341,6 +25341,516 @@
       <c r="K487" s="3" t="inlineStr">
         <is>
           <t>⚡ Production Code &amp; Architecture: EdgeRuntimeHQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="20" customHeight="1">
+      <c r="A488" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>site-1</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>LocalAgentStack</t>
+        </is>
+      </c>
+      <c r="D488" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/digitalcreatoravi-seo-engine/inference/vllm-multi-gpu-tensor-parallel-docker/</t>
+        </is>
+      </c>
+      <c r="E488" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/beebb64abf02a2d92e2d087565b245d1</t>
+        </is>
+      </c>
+      <c r="F488" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="n">
+        <v>642</v>
+      </c>
+      <c r="J488" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K488" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: LocalAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="20" customHeight="1">
+      <c r="A489" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>site-2</t>
+        </is>
+      </c>
+      <c r="C489" s="3" t="inlineStr">
+        <is>
+          <t>WorkationRadar</t>
+        </is>
+      </c>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>https://jibranpcccc.github.io/workationradar/split-croatia-coliving-guide/</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/4bc53061818975b53f95fcb79bad77f0</t>
+        </is>
+      </c>
+      <c r="F489" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="J489" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K489" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: WorkationRadar</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="20" customHeight="1">
+      <c r="A490" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>site-3</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>OpenAgentStack</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>https://openagentstack.pages.dev/frameworks/langgraph-vs-crewai-vs-autogen-multi-agent-benchmark-2026/</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/3d58f77bf0a30c9282db29c6838a13ff</t>
+        </is>
+      </c>
+      <c r="F490" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="J490" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K490" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: OpenAgentStack</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="20" customHeight="1">
+      <c r="A491" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>site-4</t>
+        </is>
+      </c>
+      <c r="C491" s="3" t="inlineStr">
+        <is>
+          <t>IndieStackAudit</t>
+        </is>
+      </c>
+      <c r="D491" s="3" t="inlineStr">
+        <is>
+          <t>https://indiestackaudit.pages.dev/billing/stripe-vs-lemonsqueezy-vs-polar-saas-fee-calculator-2026/</t>
+        </is>
+      </c>
+      <c r="E491" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/f1a9f03a7ac4186db76154f887db47ec</t>
+        </is>
+      </c>
+      <c r="F491" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="n">
+        <v>696</v>
+      </c>
+      <c r="J491" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K491" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: IndieStackAudit</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="20" customHeight="1">
+      <c r="A492" s="2" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>site-5</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>VectorBench</t>
+        </is>
+      </c>
+      <c r="D492" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorbench-hq.netlify.app/chroma-vs-lancedb-embedded-vector-db/</t>
+        </is>
+      </c>
+      <c r="E492" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/0f4ed1059317622a848d40dbb2a7836a</t>
+        </is>
+      </c>
+      <c r="F492" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="J492" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K492" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: VectorBench</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="20" customHeight="1">
+      <c r="A493" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>site-6</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>NomadTreaty</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>https://nomadtreaty.vercel.app/spain-digital-nomad-visa-beckham-law-guide/</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/3da95b20b1ef514f995f3105003c76f4</t>
+        </is>
+      </c>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="J493" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K493" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: NomadTreaty</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="20" customHeight="1">
+      <c r="A494" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>site-7</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>WebhookWatch</t>
+        </is>
+      </c>
+      <c r="D494" s="3" t="inlineStr">
+        <is>
+          <t>https://webhookwatch.vercel.app/webhook-dead-letter-queue-architecture-sqs/</t>
+        </is>
+      </c>
+      <c r="E494" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/b7d0683be4cc41eedb14c0f1cbf47f99</t>
+        </is>
+      </c>
+      <c r="F494" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="J494" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K494" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: WebhookWatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="20" customHeight="1">
+      <c r="A495" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>site-8</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>LocalDocPrivacy</t>
+        </is>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>https://localdocprivacy.netlify.app/in-browser-ocr-tesseract-wasm-guide/</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/e4eed350fca6e2bee62cf8e9b9e1b04f</t>
+        </is>
+      </c>
+      <c r="F495" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="J495" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K495" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: LocalDocPrivacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="20" customHeight="1">
+      <c r="A496" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>site-9</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>FounderRunway</t>
+        </is>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>https://site-9-inky.vercel.app/top-latin-america-tech-hubs-for-bootstrappers/</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/6d9098d38bb8b61710cfd07417efcb7f</t>
+        </is>
+      </c>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="J496" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K496" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: FounderRunway</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="20" customHeight="1">
+      <c r="A497" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>site-10</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>RAGInspect</t>
+        </is>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>https://raginspect.pages.dev/colpali-vs-bge-m3-multimodal-rag-benchmark/</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>https://gist.github.com/jibranpcccc/071ad479bb07c93922b2883c7871707b</t>
+        </is>
+      </c>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Gist Wave 4 (DA 96)</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="J497" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K497" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Production Code &amp; Benchmarks: RAGInspect</t>
         </is>
       </c>
     </row>
@@ -25487,7 +25997,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>2</v>
@@ -25508,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
@@ -25545,7 +26055,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>2</v>
@@ -25566,7 +26076,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
@@ -26125,7 +26635,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>2</v>
@@ -26146,7 +26656,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
@@ -26763,7 +27273,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>2</v>
@@ -26784,7 +27294,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
@@ -26879,7 +27389,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>2</v>
@@ -26900,7 +27410,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
@@ -26937,7 +27447,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>2</v>
@@ -26958,7 +27468,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
@@ -26995,7 +27505,7 @@
         <v>2</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>2</v>
@@ -27016,7 +27526,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P28" s="5" t="inlineStr">
         <is>
@@ -27053,7 +27563,7 @@
         <v>2</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>2</v>
@@ -27074,7 +27584,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P29" s="5" t="inlineStr">
         <is>
@@ -27111,7 +27621,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>2</v>
@@ -27132,7 +27642,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P30" s="5" t="inlineStr">
         <is>
@@ -27169,7 +27679,7 @@
         <v>2</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>2</v>
@@ -27190,7 +27700,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P31" s="5" t="inlineStr">
         <is>
@@ -28026,7 +28536,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:24:55 UTC</t>
+          <t>2026-09-12 07:23:59 UTC</t>
         </is>
       </c>
     </row>
@@ -28049,7 +28559,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -28084,7 +28594,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>100.0% (486/486 Verified HTTP 200/202)</t>
+          <t>100.0% (496/496 Verified HTTP 200/202)</t>
         </is>
       </c>
     </row>
@@ -28096,7 +28606,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>577 ms</t>
+          <t>580 ms</t>
         </is>
       </c>
     </row>
